--- a/datos/T02.xlsx
+++ b/datos/T02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BF84F6-DE0D-D64F-9399-AB760A19AA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF90670-D862-B64C-BDD8-E9E6C1D11F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="860">
   <si>
     <t>Pregunta</t>
   </si>
@@ -2616,6 +2616,9 @@
   </si>
   <si>
     <t>imagenes/cocherrojo.png</t>
+  </si>
+  <si>
+    <t>Ninguno de los dos</t>
   </si>
 </sst>
 </file>
@@ -4954,9 +4957,12 @@
         <v>446</v>
       </c>
       <c r="D112" t="s">
+        <v>859</v>
+      </c>
+      <c r="E112" t="s">
         <v>10</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>447</v>
       </c>
     </row>

--- a/datos/T02.xlsx
+++ b/datos/T02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF90670-D862-B64C-BDD8-E9E6C1D11F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9185100D-F57D-B34D-820A-038A557AD0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="861">
   <si>
     <t>Pregunta</t>
   </si>
@@ -2619,6 +2619,9 @@
   </si>
   <si>
     <t>Ninguno de los dos</t>
+  </si>
+  <si>
+    <t>imágenes/260820A.png</t>
   </si>
 </sst>
 </file>
@@ -5312,6 +5315,9 @@
       <c r="E131" t="s">
         <v>15</v>
       </c>
+      <c r="F131" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
